--- a/results/02_taxa_assemblage/LDA_Method/ModelCompar/tables/cv_confusion_matrices_combined.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelCompar/tables/cv_confusion_matrices_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model A (fully trained on 35 core sites); 5-fold x 10 cross-validation</t>
+          <t>Model A (fully trained on 25 core sites); 5-fold x 10 cross-validation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -468,17 +468,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
-      </c>
-      <c r="E3" t="n">
-        <v>44</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -487,58 +485,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
-      </c>
-      <c r="E4" t="n">
         <v>57</v>
       </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Cluster C3</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
-      </c>
-      <c r="E5" t="n">
-        <v>102</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
-      </c>
-      <c r="C6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D6" t="n">
-        <v>129</v>
-      </c>
-      <c r="E6" t="n">
-        <v>203</v>
-      </c>
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Model B (fully trained on 25 core + 23 peripheral sites); 5-fold x 10 cross-validation</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -547,92 +533,92 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Model B (fully trained on 35 core + 10 peripheral sites); 5-fold x 10 cross-validation</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>Cluster C1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>83</v>
+      </c>
+      <c r="C8" t="n">
+        <v>264</v>
+      </c>
+      <c r="D8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Cluster C1</t>
+          <t>Cluster C2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Cluster C2</t>
+          <t>Cluster C3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Cluster C3</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
+        <v>368</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>44</v>
-      </c>
-      <c r="C12" t="n">
-        <v>188</v>
-      </c>
-      <c r="D12" t="n">
-        <v>120</v>
-      </c>
-      <c r="E12" t="n">
-        <v>142</v>
-      </c>
+      <c r="A12" s="1" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Model C (fully trained on 25 core + 23 peripheral sites, weighted); 5-fold x 10 cross-validation</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -641,92 +627,92 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Model C (fully trained on 35 core + 10 peripheral sites, weighted); 5-fold x 10 cross-validation</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>Cluster C1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>67</v>
+      </c>
+      <c r="C14" t="n">
+        <v>213</v>
+      </c>
+      <c r="D14" t="n">
+        <v>63</v>
+      </c>
+      <c r="E14" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Cluster C1</t>
+          <t>Cluster C2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="E15" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Cluster C2</t>
+          <t>Cluster C3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Cluster C3</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>278</v>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>44</v>
-      </c>
-      <c r="C18" t="n">
-        <v>80</v>
-      </c>
-      <c r="D18" t="n">
-        <v>158</v>
-      </c>
-      <c r="E18" t="n">
-        <v>212</v>
-      </c>
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr"/>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Model D (fully trained on 25 core + 23 peripheral + 2 uncertain sites); 5-fold x 10 cross-validation</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -735,88 +721,77 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Model D (fully trained on 35 core + 10 peripheral + 5 uncertain sites); 5-fold x 10 cross-validation</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>Cluster C1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>83</v>
+      </c>
+      <c r="C20" t="n">
+        <v>259</v>
+      </c>
+      <c r="D20" t="n">
+        <v>34</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Cluster C1</t>
+          <t>Cluster C2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Cluster C2</t>
+          <t>Cluster C3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Cluster C3</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C23" t="n">
-        <v>88</v>
+        <v>371</v>
       </c>
       <c r="D23" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="E23" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>45</v>
-      </c>
-      <c r="C24" t="n">
-        <v>231</v>
-      </c>
-      <c r="D24" t="n">
-        <v>115</v>
-      </c>
-      <c r="E24" t="n">
-        <v>154</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
